--- a/Unity/Assets/Config/Excel/StoryChoiceConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryChoiceConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -109,10 +109,31 @@
     <t>谢谢你没有放弃我</t>
   </si>
   <si>
+    <t>1;200</t>
+  </si>
+  <si>
     <t>给他一拳</t>
   </si>
   <si>
     <t>cnm</t>
+  </si>
+  <si>
+    <t>1;300</t>
+  </si>
+  <si>
+    <t>等于2</t>
+  </si>
+  <si>
+    <t>真聪明</t>
+  </si>
+  <si>
+    <t>等于3</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>等于4</t>
   </si>
 </sst>
 </file>
@@ -11299,7 +11320,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{5C1CDFEB-75F6-4C75-814B-1C696F7516E7}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{1572DEAF-0441-4572-A885-836A46139A2A}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11599,8 +11620,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
     <col min="3" max="4" width="22" style="3" customWidth="1"/>
@@ -11745,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -11753,10 +11774,10 @@
         <v>10013</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -11768,7 +11789,214 @@
         <v>3</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:8">
+      <c r="B8" s="2">
+        <v>10021</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:8">
+      <c r="B9" s="2">
+        <v>10022</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:8">
+      <c r="B10" s="2">
+        <v>10023</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:8">
+      <c r="B11" s="2">
+        <v>20011</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:8">
+      <c r="B12" s="2">
+        <v>20012</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:8">
+      <c r="B13" s="2">
+        <v>20013</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:8">
+      <c r="B14" s="2">
+        <v>20021</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:8">
+      <c r="B15" s="2">
+        <v>20022</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:8">
+      <c r="B16" s="2">
+        <v>20023</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/StoryChoiceConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryChoiceConfig.xlsx
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -11843,7 +11843,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -11875,7 +11875,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>0</v>
@@ -12365,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -12397,7 +12397,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -12658,7 +12658,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
